--- a/data/ECC_Erie_P_loading/total-p-loading-lake-erie-2008-2020_calculation.xlsx
+++ b/data/ECC_Erie_P_loading/total-p-loading-lake-erie-2008-2020_calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/data/ECC_Erie_P_loading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{42FCA07D-2E64-4A2C-91F8-5D56572CFFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{549AFD93-E5D9-4AD8-9B43-C06ABB9F3E9B}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{42FCA07D-2E64-4A2C-91F8-5D56572CFFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C75A5B-FAB1-42CA-8CE5-108D7A06EACE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="340" yWindow="1800" windowWidth="14400" windowHeight="7280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="total-p-loading-lake-erie-2008-" sheetId="1" r:id="rId1"/>
@@ -235,7 +235,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +413,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -576,8 +582,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1268,7 +1275,7 @@
       <c r="D14">
         <v>11661</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
@@ -1282,7 +1289,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>2019</v>
       </c>
       <c r="B15">
@@ -1291,7 +1298,7 @@
       <c r="C15">
         <v>2599</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>13544</v>
       </c>
       <c r="F15">
@@ -1302,7 +1309,7 @@
         <f>0.297*D15</f>
         <v>4022.5679999999998</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <f>0.33*D15</f>
         <v>4469.5200000000004</v>
       </c>
